--- a/reports/20260507/API_Upload_Real_Attachment_claude.xlsx
+++ b/reports/20260507/API_Upload_Real_Attachment_claude.xlsx
@@ -562,7 +562,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>candidateId=1753</t>
+          <t>candidateId=1805</t>
         </is>
       </c>
     </row>
@@ -609,7 +609,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>candidateId=1755</t>
+          <t>candidateId=1811</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>status=OK, code=None, AttachmentId=439</t>
+          <t>status=OK, code=None, AttachmentId=455</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>status=OK, AttachmentId=441</t>
+          <t>status=OK, AttachmentId=457</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1596,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>status=OK, deleted=[439, 441]</t>
+          <t>status=OK, deleted=[455, 457]</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>status=OK, AttachmentId=443</t>
+          <t>status=OK, AttachmentId=459</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>1st=OK/id=445, 2nd=OK/id=447</t>
+          <t>1st=OK/id=461, 2nd=OK/id=463</t>
         </is>
       </c>
     </row>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>status=OK, AttachmentId=449</t>
+          <t>status=OK, AttachmentId=465</t>
         </is>
       </c>
     </row>
@@ -2724,7 +2724,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>status=OK, deleted=[443, 445, 447, 449]</t>
+          <t>status=OK, deleted=[459, 461, 463, 465]</t>
         </is>
       </c>
     </row>
